--- a/Config/GameConfig/Datas/worker.xlsx
+++ b/Config/GameConfig/Datas/worker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Configs\GameConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B800CF86-775B-4B04-B37D-F21E7CEF4DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8646A5-A5B1-4688-A82E-75A3024E1095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="2610" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -203,22 +203,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>item.EQuality</t>
-  </si>
-  <si>
     <t>品质</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>WHITE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>GREEN</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>quality</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -639,7 +632,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -707,7 +700,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -777,7 +770,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>13</v>
@@ -813,13 +806,13 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6">
-        <v>1010001</v>
+        <v>2000001</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>34</v>
+      <c r="D6" s="4">
+        <v>0</v>
       </c>
       <c r="F6">
         <v>110</v>
@@ -845,13 +838,13 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B7">
-        <v>1010002</v>
+        <v>2000002</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>35</v>
+      <c r="D7" s="4">
+        <v>1</v>
       </c>
       <c r="F7">
         <v>120</v>
@@ -877,13 +870,13 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B8">
-        <v>1010003</v>
+        <v>2000003</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>35</v>
+      <c r="D8" s="4">
+        <v>1</v>
       </c>
       <c r="F8">
         <v>130</v>
@@ -909,13 +902,13 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B9">
-        <v>1010004</v>
+        <v>2000004</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>35</v>
+      <c r="D9" s="4">
+        <v>1</v>
       </c>
       <c r="F9">
         <v>140</v>
@@ -941,13 +934,13 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B10">
-        <v>1010005</v>
+        <v>2000005</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>35</v>
+      <c r="D10" s="4">
+        <v>1</v>
       </c>
       <c r="F10">
         <v>150</v>
